--- a/data/trans_camb/IP1009-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1009-Provincia-trans_camb.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,25</t>
+          <t>0,0; 5,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,16</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,92</t>
+          <t>0,0; 3,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,67</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,28</t>
+          <t>0,0; 5,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,22</t>
+          <t>0,0; 2,68</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,52</t>
+          <t>0,0; 5,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,96</t>
+          <t>0,0; 5,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1114,17 +1114,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,69</t>
+          <t>0,0; 4,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 2,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,07</t>
+          <t>0,0; 3,15</t>
         </is>
       </c>
     </row>
@@ -1265,22 +1265,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,72; 0,0</t>
+          <t>-9,0; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,89; 0,0</t>
+          <t>-6,27; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 0,0</t>
+          <t>-4,53; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 0,0</t>
+          <t>-4,03; 0,0</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1519,7 +1519,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,77</t>
+          <t>0,0; 2,7</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,8</t>
+          <t>0,0; 3,34</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 0,0</t>
+          <t>-2,49; 0,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 0,0</t>
+          <t>-2,49; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,47</t>
+          <t>-0,77; 0,47</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,83</t>
+          <t>-0,52; 0,84</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 0,0</t>
+          <t>-2,57; 0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,22</t>
+          <t>-1,52; 1,13</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 0,0</t>
+          <t>-2,55; 0,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,69</t>
+          <t>-1,66; 0,69</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,49; -0,14</t>
+          <t>-1,36; -0,14</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 0,69</t>
+          <t>-1,0; 0,72</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,4</t>
+          <t>-0,26; 0,44</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 0,75</t>
+          <t>-0,14; 0,7</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 0,07</t>
+          <t>-0,68; 0,07</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,57</t>
+          <t>-0,39; 0,53</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 0,16</t>
+          <t>-0,37; 0,13</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 0,49</t>
+          <t>-0,17; 0,49</t>
         </is>
       </c>
     </row>
@@ -1970,17 +1970,17 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 202,88</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-51,25; 648,18</t>
+          <t>-60,3; 502,34</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1009-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1009-Provincia-trans_camb.xlsx
@@ -641,7 +641,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,2</t>
+          <t>0,0; 4,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 2,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,27</t>
+          <t>0,0; 3,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,87</t>
         </is>
       </c>
     </row>
@@ -958,7 +958,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,25</t>
+          <t>0,0; 6,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,68</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,47</t>
+          <t>0,0; 5,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,43</t>
+          <t>0,0; 4,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,04</t>
+          <t>0,0; 4,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,15</t>
+          <t>0,0; 3,05</t>
         </is>
       </c>
     </row>
@@ -1265,22 +1265,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 0,0</t>
+          <t>-7,83; 0,0</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 0,0</t>
+          <t>-7,83; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 0,0</t>
+          <t>-4,03; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 0,0</t>
+          <t>-4,04; 0,0</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,7</t>
+          <t>0,0; 2,9</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,34</t>
+          <t>0,0; 2,84</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,0</t>
+          <t>-2,55; 0,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,0</t>
+          <t>-3,14; 0,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 0,47</t>
+          <t>-1,02; 0,47</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,84</t>
+          <t>-0,52; 1,09</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 0,0</t>
+          <t>-2,2; 0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 1,13</t>
+          <t>-1,42; 1,24</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 0,0</t>
+          <t>-2,24; 0,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 0,69</t>
+          <t>-1,35; 0,69</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,36; -0,14</t>
+          <t>-1,55; -0,14</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 0,72</t>
+          <t>-1,01; 0,68</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,44</t>
+          <t>-0,26; 0,37</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 0,7</t>
+          <t>-0,15; 0,72</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,07</t>
+          <t>-0,67; 0,08</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,53</t>
+          <t>-0,4; 0,55</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,13</t>
+          <t>-0,38; 0,12</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 0,49</t>
+          <t>-0,18; 0,47</t>
         </is>
       </c>
     </row>
@@ -1970,17 +1970,17 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 202,88</t>
+          <t>-100,0; 192,71</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-60,3; 502,34</t>
+          <t>-62,09; 505,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1009-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP1009-Provincia-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,17 +593,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,02</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,02</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,77</t>
+          <t>0,0; 3,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -669,17 +669,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -754,17 +754,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>0,65</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,65</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,87</t>
+          <t>0,0; 1,67</t>
         </is>
       </c>
     </row>
@@ -830,17 +830,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -910,17 +910,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>1,05</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,05</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -948,7 +948,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,0; 3,22</t>
         </is>
       </c>
     </row>
@@ -986,17 +986,17 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>0,82</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,82</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,98</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,82</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,77</t>
+          <t>0,0; 4,69</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,19</t>
+          <t>0,0; 5,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,01</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,05</t>
+          <t>0,0; 3,07</t>
         </is>
       </c>
     </row>
@@ -1137,17 +1137,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,56</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,56</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-1,56</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,56</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,72; 0,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-7,89; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 0,0</t>
+          <t>-4,84; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 0,0</t>
+          <t>-4,09; 0,0</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,5</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,5</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>0,48</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>0,56</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-0,5</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,5</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,9</t>
+          <t>-2,52; 0,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,84</t>
+          <t>-2,52; 0,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 0,0</t>
+          <t>0,0; 2,77</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 0,0</t>
+          <t>0,0; 2,8</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,47</t>
+          <t>-0,99; 0,47</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 1,09</t>
+          <t>-0,52; 0,83</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1685,22 +1685,22 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-0,42</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-0,08</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>-0,68</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>-0,04</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-0,42</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-0,08</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,0</t>
+          <t>-1,93; 0,0</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 1,24</t>
+          <t>-1,32; 0,69</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,0</t>
+          <t>-2,27; 0,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,69</t>
+          <t>-1,56; 1,22</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,55; -0,14</t>
+          <t>-1,49; -0,14</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,68</t>
+          <t>-1,0; 0,69</t>
         </is>
       </c>
     </row>
@@ -1766,17 +1766,17 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>-18,75%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-5,72%</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-18,75%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1841,22 +1841,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-0,2</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>0,08</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>0,03</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>0,21</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-0,2</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>0,08</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,37</t>
+          <t>-0,76; 0,07</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 0,72</t>
+          <t>-0,47; 0,57</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,08</t>
+          <t>-0,28; 0,4</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,55</t>
+          <t>-0,15; 0,75</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,12</t>
+          <t>-0,34; 0,16</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,47</t>
+          <t>-0,16; 0,49</t>
         </is>
       </c>
     </row>
@@ -1917,22 +1917,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-71,11%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>26,57%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>16,05%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>131,08%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-71,11%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>26,57%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 192,71</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-62,09; 505,12</t>
+          <t>-51,25; 648,18</t>
         </is>
       </c>
     </row>
